--- a/PartialRefund.xlsx
+++ b/PartialRefund.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909EC397-D17B-4960-B138-51035A766958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E91946-5C26-4AAD-B61A-9E8FA241E460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="2670" windowWidth="31880" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SaleAndPartialRefund" sheetId="1" r:id="rId1"/>
@@ -537,10 +537,10 @@
     <t>The specified refund amount is greater than what is allowed for the payment</t>
   </si>
   <si>
-    <t>12/25</t>
-  </si>
-  <si>
     <t>iahmed@govolution.com</t>
+  </si>
+  <si>
+    <t>12/29</t>
   </si>
 </sst>
 </file>
@@ -597,10 +597,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -882,83 +881,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BX26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="58" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="6.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="5.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="9.15234375" style="1"/>
-    <col min="41" max="41" width="8.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="14.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="6.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.1328125" style="1"/>
+    <col min="41" max="41" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="12.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="11.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="5.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="31.84375" style="1" customWidth="1"/>
-    <col min="57" max="57" width="14.3828125" style="1" customWidth="1"/>
-    <col min="58" max="58" width="16.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="31.86328125" style="1" customWidth="1"/>
+    <col min="57" max="57" width="14.3984375" style="1" customWidth="1"/>
+    <col min="58" max="58" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="14.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="14.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="12.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13.84375" style="1" customWidth="1"/>
+    <col min="63" max="63" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.86328125" style="1" customWidth="1"/>
     <col min="65" max="65" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="17.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="14.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="35.69140625" style="1" customWidth="1"/>
-    <col min="72" max="72" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="7.69140625" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9.15234375" style="1"/>
+    <col min="66" max="66" width="10.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="17.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="14.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="35.6640625" style="1" customWidth="1"/>
+    <col min="72" max="72" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="7.6640625" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +1187,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
@@ -1243,8 +1242,8 @@
       <c r="BB2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD2" s="2" t="s">
-        <v>171</v>
+      <c r="BD2" t="s">
+        <v>170</v>
       </c>
       <c r="BE2" s="1">
         <v>22201</v>
@@ -1253,7 +1252,7 @@
         <v>145</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>83</v>
@@ -1283,7 +1282,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
@@ -1338,8 +1337,8 @@
       <c r="BB3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD3" s="2" t="s">
-        <v>171</v>
+      <c r="BD3" t="s">
+        <v>170</v>
       </c>
       <c r="BE3" s="1">
         <v>123456789</v>
@@ -1348,7 +1347,7 @@
         <v>145</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO3" s="1" t="s">
         <v>83</v>
@@ -1378,7 +1377,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>129</v>
       </c>
@@ -1433,8 +1432,8 @@
       <c r="BB4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD4" s="2" t="s">
-        <v>171</v>
+      <c r="BD4" t="s">
+        <v>170</v>
       </c>
       <c r="BE4" s="1" t="s">
         <v>88</v>
@@ -1443,7 +1442,7 @@
         <v>145</v>
       </c>
       <c r="BN4" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO4" s="1" t="s">
         <v>83</v>
@@ -1473,7 +1472,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
@@ -1531,8 +1530,8 @@
       <c r="BB5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD5" s="2" t="s">
-        <v>171</v>
+      <c r="BD5" t="s">
+        <v>170</v>
       </c>
       <c r="BE5" s="1">
         <v>22201</v>
@@ -1541,7 +1540,7 @@
         <v>145</v>
       </c>
       <c r="BN5" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO5" s="1" t="s">
         <v>83</v>
@@ -1571,7 +1570,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>131</v>
       </c>
@@ -1629,8 +1628,8 @@
       <c r="BB6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD6" s="2" t="s">
-        <v>171</v>
+      <c r="BD6" t="s">
+        <v>170</v>
       </c>
       <c r="BE6" s="1">
         <v>123456789</v>
@@ -1639,7 +1638,7 @@
         <v>145</v>
       </c>
       <c r="BN6" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO6" s="1" t="s">
         <v>83</v>
@@ -1669,7 +1668,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>132</v>
       </c>
@@ -1727,8 +1726,8 @@
       <c r="BB7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD7" s="2" t="s">
-        <v>171</v>
+      <c r="BD7" t="s">
+        <v>170</v>
       </c>
       <c r="BE7" s="1" t="s">
         <v>88</v>
@@ -1737,7 +1736,7 @@
         <v>145</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO7" s="1" t="s">
         <v>83</v>
@@ -1767,7 +1766,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>133</v>
       </c>
@@ -1825,8 +1824,8 @@
       <c r="BB8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD8" s="2" t="s">
-        <v>171</v>
+      <c r="BD8" t="s">
+        <v>170</v>
       </c>
       <c r="BE8" s="1" t="s">
         <v>97</v>
@@ -1835,7 +1834,7 @@
         <v>145</v>
       </c>
       <c r="BN8" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO8" s="1" t="s">
         <v>83</v>
@@ -1865,7 +1864,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>134</v>
       </c>
@@ -1923,8 +1922,8 @@
       <c r="BB9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD9" s="2" t="s">
-        <v>171</v>
+      <c r="BD9" t="s">
+        <v>170</v>
       </c>
       <c r="BE9" s="1" t="s">
         <v>98</v>
@@ -1933,7 +1932,7 @@
         <v>145</v>
       </c>
       <c r="BN9" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO9" s="1" t="s">
         <v>83</v>
@@ -1963,7 +1962,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>135</v>
       </c>
@@ -2021,8 +2020,8 @@
       <c r="BB10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD10" s="2" t="s">
-        <v>171</v>
+      <c r="BD10" t="s">
+        <v>170</v>
       </c>
       <c r="BE10" s="1" t="s">
         <v>99</v>
@@ -2031,7 +2030,7 @@
         <v>145</v>
       </c>
       <c r="BN10" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO10" s="1" t="s">
         <v>83</v>
@@ -2061,7 +2060,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>136</v>
       </c>
@@ -2119,8 +2118,8 @@
       <c r="BB11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD11" s="2" t="s">
-        <v>171</v>
+      <c r="BD11" t="s">
+        <v>170</v>
       </c>
       <c r="BE11" s="1" t="s">
         <v>100</v>
@@ -2129,7 +2128,7 @@
         <v>145</v>
       </c>
       <c r="BN11" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO11" s="1" t="s">
         <v>83</v>
@@ -2159,7 +2158,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>137</v>
       </c>
@@ -2214,8 +2213,8 @@
       <c r="BB12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="BD12" s="2" t="s">
-        <v>171</v>
+      <c r="BD12" t="s">
+        <v>170</v>
       </c>
       <c r="BE12" s="1">
         <v>22201</v>
@@ -2224,7 +2223,7 @@
         <v>145</v>
       </c>
       <c r="BN12" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO12" s="1" t="s">
         <v>83</v>
@@ -2254,7 +2253,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>138</v>
       </c>
@@ -2309,8 +2308,8 @@
       <c r="BB13" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BD13" s="2" t="s">
-        <v>171</v>
+      <c r="BD13" t="s">
+        <v>170</v>
       </c>
       <c r="BE13" s="1">
         <v>22201</v>
@@ -2319,7 +2318,7 @@
         <v>145</v>
       </c>
       <c r="BN13" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO13" s="1" t="s">
         <v>83</v>
@@ -2349,7 +2348,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>139</v>
       </c>
@@ -2404,8 +2403,8 @@
       <c r="BB14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD14" s="2" t="s">
-        <v>171</v>
+      <c r="BD14" t="s">
+        <v>170</v>
       </c>
       <c r="BE14" s="1">
         <v>22201</v>
@@ -2414,7 +2413,7 @@
         <v>145</v>
       </c>
       <c r="BN14" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO14" s="1" t="s">
         <v>83</v>
@@ -2444,7 +2443,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>140</v>
       </c>
@@ -2499,8 +2498,8 @@
       <c r="BB15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD15" s="2" t="s">
-        <v>171</v>
+      <c r="BD15" t="s">
+        <v>170</v>
       </c>
       <c r="BE15" s="1">
         <v>123456789</v>
@@ -2509,7 +2508,7 @@
         <v>145</v>
       </c>
       <c r="BN15" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO15" s="1" t="s">
         <v>83</v>
@@ -2539,7 +2538,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>141</v>
       </c>
@@ -2594,8 +2593,8 @@
       <c r="BB16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD16" s="2" t="s">
-        <v>171</v>
+      <c r="BD16" t="s">
+        <v>170</v>
       </c>
       <c r="BE16" s="1" t="s">
         <v>88</v>
@@ -2604,7 +2603,7 @@
         <v>145</v>
       </c>
       <c r="BN16" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO16" s="1" t="s">
         <v>83</v>
@@ -2634,7 +2633,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>142</v>
       </c>
@@ -2692,8 +2691,8 @@
       <c r="BB17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD17" s="2" t="s">
-        <v>171</v>
+      <c r="BD17" t="s">
+        <v>170</v>
       </c>
       <c r="BE17" s="1">
         <v>22201</v>
@@ -2702,7 +2701,7 @@
         <v>145</v>
       </c>
       <c r="BN17" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO17" s="1" t="s">
         <v>83</v>
@@ -2732,7 +2731,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>143</v>
       </c>
@@ -2790,8 +2789,8 @@
       <c r="BB18" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD18" s="2" t="s">
-        <v>171</v>
+      <c r="BD18" t="s">
+        <v>170</v>
       </c>
       <c r="BE18" s="1">
         <v>123456789</v>
@@ -2800,7 +2799,7 @@
         <v>145</v>
       </c>
       <c r="BN18" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO18" s="1" t="s">
         <v>83</v>
@@ -2830,7 +2829,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>144</v>
       </c>
@@ -2888,8 +2887,8 @@
       <c r="BB19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD19" s="2" t="s">
-        <v>171</v>
+      <c r="BD19" t="s">
+        <v>170</v>
       </c>
       <c r="BE19" s="1" t="s">
         <v>88</v>
@@ -2898,7 +2897,7 @@
         <v>145</v>
       </c>
       <c r="BN19" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO19" s="1" t="s">
         <v>83</v>
@@ -2928,7 +2927,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>145</v>
       </c>
@@ -2986,8 +2985,8 @@
       <c r="BB20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD20" s="2" t="s">
-        <v>171</v>
+      <c r="BD20" t="s">
+        <v>170</v>
       </c>
       <c r="BE20" s="1" t="s">
         <v>97</v>
@@ -2996,7 +2995,7 @@
         <v>145</v>
       </c>
       <c r="BN20" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO20" s="1" t="s">
         <v>83</v>
@@ -3026,7 +3025,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>146</v>
       </c>
@@ -3084,8 +3083,8 @@
       <c r="BB21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD21" s="2" t="s">
-        <v>171</v>
+      <c r="BD21" t="s">
+        <v>170</v>
       </c>
       <c r="BE21" s="1" t="s">
         <v>98</v>
@@ -3094,7 +3093,7 @@
         <v>145</v>
       </c>
       <c r="BN21" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO21" s="1" t="s">
         <v>83</v>
@@ -3124,7 +3123,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>147</v>
       </c>
@@ -3182,8 +3181,8 @@
       <c r="BB22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD22" s="2" t="s">
-        <v>171</v>
+      <c r="BD22" t="s">
+        <v>170</v>
       </c>
       <c r="BE22" s="1" t="s">
         <v>99</v>
@@ -3192,7 +3191,7 @@
         <v>145</v>
       </c>
       <c r="BN22" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO22" s="1" t="s">
         <v>83</v>
@@ -3222,7 +3221,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
@@ -3280,8 +3279,8 @@
       <c r="BB23" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD23" s="2" t="s">
-        <v>171</v>
+      <c r="BD23" t="s">
+        <v>170</v>
       </c>
       <c r="BE23" s="1" t="s">
         <v>100</v>
@@ -3290,7 +3289,7 @@
         <v>145</v>
       </c>
       <c r="BN23" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO23" s="1" t="s">
         <v>83</v>
@@ -3320,7 +3319,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -3375,8 +3374,8 @@
       <c r="BB24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="BD24" s="2" t="s">
-        <v>171</v>
+      <c r="BD24" t="s">
+        <v>170</v>
       </c>
       <c r="BE24" s="1">
         <v>22201</v>
@@ -3385,7 +3384,7 @@
         <v>145</v>
       </c>
       <c r="BN24" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO24" s="1" t="s">
         <v>83</v>
@@ -3415,7 +3414,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>150</v>
       </c>
@@ -3470,8 +3469,8 @@
       <c r="BB25" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BD25" s="2" t="s">
-        <v>171</v>
+      <c r="BD25" t="s">
+        <v>170</v>
       </c>
       <c r="BE25" s="1">
         <v>22201</v>
@@ -3480,7 +3479,7 @@
         <v>145</v>
       </c>
       <c r="BN25" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO25" s="1" t="s">
         <v>83</v>
@@ -3510,7 +3509,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:76" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>166</v>
       </c>
@@ -3565,8 +3564,8 @@
       <c r="BB26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BD26" s="2" t="s">
-        <v>171</v>
+      <c r="BD26" t="s">
+        <v>170</v>
       </c>
       <c r="BE26" s="1">
         <v>22201</v>
@@ -3575,7 +3574,7 @@
         <v>145</v>
       </c>
       <c r="BN26" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BO26" s="1" t="s">
         <v>83</v>
